--- a/artfynd/A 2318-2025 artfynd.xlsx
+++ b/artfynd/A 2318-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,6 +1040,122 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122625999</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103175</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222005</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Strandviol</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Viola stagnina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kit. ex Schult</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stora Bringes 1,25 km V, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>716553</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6379115</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>I-Got-2017</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1990-01-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1994-12-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bringes 5:1</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars-Åke Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2318-2025 artfynd.xlsx
+++ b/artfynd/A 2318-2025 artfynd.xlsx
@@ -1045,7 +1045,7 @@
         <v>122625999</v>
       </c>
       <c r="B5" t="n">
-        <v>103175</v>
+        <v>103178</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 2318-2025 artfynd.xlsx
+++ b/artfynd/A 2318-2025 artfynd.xlsx
@@ -1045,7 +1045,7 @@
         <v>122625999</v>
       </c>
       <c r="B5" t="n">
-        <v>103178</v>
+        <v>103179</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 2318-2025 artfynd.xlsx
+++ b/artfynd/A 2318-2025 artfynd.xlsx
@@ -1045,7 +1045,7 @@
         <v>122625999</v>
       </c>
       <c r="B5" t="n">
-        <v>103179</v>
+        <v>103182</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 2318-2025 artfynd.xlsx
+++ b/artfynd/A 2318-2025 artfynd.xlsx
@@ -1045,7 +1045,7 @@
         <v>122625999</v>
       </c>
       <c r="B5" t="n">
-        <v>103182</v>
+        <v>103285</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 2318-2025 artfynd.xlsx
+++ b/artfynd/A 2318-2025 artfynd.xlsx
@@ -1045,7 +1045,7 @@
         <v>122625999</v>
       </c>
       <c r="B5" t="n">
-        <v>103285</v>
+        <v>103293</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 2318-2025 artfynd.xlsx
+++ b/artfynd/A 2318-2025 artfynd.xlsx
@@ -1045,7 +1045,7 @@
         <v>122625999</v>
       </c>
       <c r="B5" t="n">
-        <v>103293</v>
+        <v>103295</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 2318-2025 artfynd.xlsx
+++ b/artfynd/A 2318-2025 artfynd.xlsx
@@ -1045,7 +1045,7 @@
         <v>122625999</v>
       </c>
       <c r="B5" t="n">
-        <v>103295</v>
+        <v>103303</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 2318-2025 artfynd.xlsx
+++ b/artfynd/A 2318-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,122 +1040,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>122625999</v>
-      </c>
-      <c r="B5" t="n">
-        <v>103303</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>222005</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Strandviol</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Viola stagnina</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Kit. ex Schult</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Stora Bringes 1,25 km V, Gtl</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>716553</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6379115</v>
-      </c>
-      <c r="S5" t="n">
-        <v>50</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Norrlanda</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>I-Got-2017</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>1990-01-01</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>1994-12-31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Bringes 5:1</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Sofia Lund</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Lars-Åke Pettersson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
